--- a/docs/1.0接口文档.xlsx
+++ b/docs/1.0接口文档.xlsx
@@ -362,7 +362,7 @@
     <t>X-Version</t>
   </si>
   <si>
-    <t>"MiddleCaller-Code-Version</t>
+    <t>MiddleCaller-Code-Version</t>
   </si>
   <si>
     <t>展示版本号</t>
